--- a/public/sample1.xlsx
+++ b/public/sample1.xlsx
@@ -179,7 +179,7 @@
     <t>名前</t>
   </si>
   <si>
-    <t>要支援</t>
+    <t>学習支援</t>
   </si>
   <si>
     <t>体育</t>
@@ -439,21 +439,21 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>不登校気味</t>
+    <t>登校支援</t>
     <rPh sb="0" eb="5">
       <t>フトウコウギミ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>弱視者</t>
+    <t>視覚配慮</t>
     <rPh sb="0" eb="3">
       <t>ジャクシシャ</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>情緒障害</t>
+    <t>情緒面の配慮</t>
     <rPh sb="0" eb="2">
       <t>ジョウチョ</t>
     </rPh>

--- a/public/sample1.xlsx
+++ b/public/sample1.xlsx
@@ -440,26 +440,14 @@
   </si>
   <si>
     <t>登校支援</t>
-    <rPh sb="0" eb="5">
-      <t>フトウコウギミ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
     <t>視覚配慮</t>
-    <rPh sb="0" eb="3">
-      <t>ジャクシシャ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>
     <t>情緒面の配慮</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウチョ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショウガイ</t>
-    </rPh>
     <phoneticPr fontId="18"/>
   </si>
   <si>

--- a/public/sample1.xlsx
+++ b/public/sample1.xlsx
@@ -179,7 +179,7 @@
     <t>名前</t>
   </si>
   <si>
-    <t>要支援</t>
+    <t>学習支援</t>
   </si>
   <si>
     <t>体育</t>
@@ -439,27 +439,15 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>不登校気味</t>
-    <rPh sb="0" eb="5">
-      <t>フトウコウギミ</t>
-    </rPh>
+    <t>登校支援</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>弱視者</t>
-    <rPh sb="0" eb="3">
-      <t>ジャクシシャ</t>
-    </rPh>
+    <t>視覚配慮</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>情緒障害</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウチョ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショウガイ</t>
-    </rPh>
+    <t>情緒面の配慮</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
